--- a/reports/demo_churn/churn_demo_cleaned.xlsx
+++ b/reports/demo_churn/churn_demo_cleaned.xlsx
@@ -212,13 +212,13 @@
     <comment ref="J48" authorId="0" shapeId="0">
       <text>
         <t>IloveCSV: UNRESOLVED (target.missing, open)
-No target label: this row cannot be used for supervised training.</t>
+No usable target label: this row cannot be used for supervised training.</t>
       </text>
     </comment>
     <comment ref="J54" authorId="0" shapeId="0">
       <text>
         <t>IloveCSV: UNRESOLVED (target.missing, open)
-No target label: this row cannot be used for supervised training.</t>
+No usable target label: this row cannot be used for supervised training.</t>
       </text>
     </comment>
     <comment ref="E60" authorId="0" shapeId="0">
